--- a/data/dividends_info_20260822.xlsx
+++ b/data/dividends_info_20260822.xlsx
@@ -1650,7 +1650,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2132,7 +2132,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2166,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2217,7 +2217,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2234,7 +2234,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2268,7 +2268,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2295,14 +2295,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2312,14 +2312,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2336,7 +2336,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2353,7 +2353,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2370,7 +2370,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2387,7 +2387,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2404,7 +2404,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2438,7 +2438,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2455,7 +2455,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2472,7 +2472,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2489,7 +2489,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2506,7 +2506,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2516,14 +2516,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2533,14 +2533,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2557,7 +2557,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2574,7 +2574,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2584,14 +2584,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2608,7 +2608,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2625,7 +2625,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2635,14 +2635,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2659,7 +2659,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2669,14 +2669,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2880,7 +2880,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2897,7 +2897,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2948,7 +2948,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2965,7 +2965,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2975,14 +2975,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2992,14 +2992,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -3025,108 +3025,6 @@
         </is>
       </c>
       <c r="C81" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>DigiTouch S.p.A.</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>DigiTouch S.p.A.</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>RT&amp;L S.P.A.</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Confinvest Oro S.p.A.</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Yakkyo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
         <is>
           <t>Half Year Report</t>
         </is>
@@ -3156,95 +3054,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Confinvest Oro S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RT&amp;L S.P.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Yakkyo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>